--- a/files/九龙-西南九龙-维港滙 I.xlsx
+++ b/files/九龙-西南九龙-维港滙 I.xlsx
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="E313" s="4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
@@ -14966,14 +14966,14 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
         <v>6556500</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>23670</v>
+        <v>23585</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
           <t>C | 493呎 (2房)
 $1,288万
 $26,119/呎
-(25年-11月)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -28097,7 +28097,7 @@
           <t>D | 448呎 (2房)
 $1,048万
 $23,393/呎
-(25年-02月)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -28255,7 +28255,7 @@
           <t>F | 320呎 (1房)
 $826万
 $25,801/呎
-(26年-03月)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
@@ -28410,10 +28410,10 @@
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>H | 277呎 (开放式)
+          <t>H | 278呎 (开放式)
 $656万
-$23,670/呎
-(26年-06月)</t>
+$23,585/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>
